--- a/data/PolicePosition.xlsx
+++ b/data/PolicePosition.xlsx
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-72.48531</v>
+        <v>-72.50083621127875</v>
       </c>
       <c r="C10" t="n">
-        <v>19.48353</v>
+        <v>19.52293197488715</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-72.3370328</v>
+        <v>-72.30515104511825</v>
       </c>
       <c r="C11" t="n">
-        <v>19.3713028</v>
+        <v>19.46275948123387</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-72.62546210815373</v>
+        <v>-72.20360240597159</v>
       </c>
       <c r="C12" t="n">
-        <v>19.31536184562747</v>
+        <v>19.15803666281501</v>
       </c>
     </row>
     <row r="13">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-72.02229033655703</v>
+        <v>-72.17053436249488</v>
       </c>
       <c r="C27" t="n">
-        <v>19.18702011326263</v>
+        <v>19.2152283835812</v>
       </c>
     </row>
     <row r="28">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-72.51560191472166</v>
+        <v>-72.52418347250948</v>
       </c>
       <c r="C32" t="n">
-        <v>18.77696953453604</v>
+        <v>18.79778186720354</v>
       </c>
     </row>
     <row r="33">
